--- a/artfynd/A 28715-2026 artfynd.xlsx
+++ b/artfynd/A 28715-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -801,6 +806,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129170800</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75452664</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96603861</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,6 +1131,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132976244</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132976227</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,6 +1353,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132976237</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1438,6 +1473,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83650942</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1544,6 +1584,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132976222</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1650,6 +1695,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132976245</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1756,6 +1806,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132976239</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1862,6 +1917,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132976246</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1968,6 +2028,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132976234</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2070,8 +2135,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129282017</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28715-2026 artfynd.xlsx
+++ b/artfynd/A 28715-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1481,27 +1481,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132976222</v>
+        <v>136441920</v>
       </c>
       <c r="B9" t="n">
-        <v>106236</v>
+        <v>107039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221141</v>
+        <v>220785</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1512,17 +1512,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ingasäter NO om, Vg</t>
+          <t>Noltorps gamla tomt, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>431593</v>
+        <v>431542</v>
       </c>
       <c r="R9" t="n">
-        <v>6484647</v>
+        <v>6484578</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1546,12 +1546,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Bohål i ask på västra sidan av vägen ca 2,5 m till väg. Omkrets uppskattningsvis åtminstone 2 m. Dålig vitalitet</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,40 +1567,35 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Lösvkogsområde</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson</t>
+          <t>Åsa Tengström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Åsa Tengström, Jennifer Gao, Denise Gunnarsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>Billingens flora</t>
+          <t>Skyddsvärda träd</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132976222</t>
+          <t>https://artportalen.se/Sighting/136441920</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132976245</v>
+        <v>132976222</v>
       </c>
       <c r="B10" t="n">
-        <v>106679</v>
+        <v>106236</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1603,21 +1603,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221570</v>
+        <v>221141</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk lungört</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pulmonaria obscura</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Dumort.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1627,10 +1627,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>431550</v>
+        <v>431593</v>
       </c>
       <c r="R10" t="n">
-        <v>6484628</v>
+        <v>6484647</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1697,16 +1697,16 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132976245</t>
+          <t>https://artportalen.se/Sighting/132976222</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132976239</v>
+        <v>132976245</v>
       </c>
       <c r="B11" t="n">
-        <v>104197</v>
+        <v>106679</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,21 +1714,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221987</v>
+        <v>221570</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsbingel</t>
+          <t>Mörk lungört</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Mercurialis perennis</t>
+          <t>Pulmonaria obscura</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Dumort.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1808,16 +1808,16 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132976239</t>
+          <t>https://artportalen.se/Sighting/132976245</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132976246</v>
+        <v>132976239</v>
       </c>
       <c r="B12" t="n">
-        <v>101403</v>
+        <v>104197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,21 +1825,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>221987</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsbingel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Mercurialis perennis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1919,16 +1919,16 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132976246</t>
+          <t>https://artportalen.se/Sighting/132976239</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132976234</v>
+        <v>132976246</v>
       </c>
       <c r="B13" t="n">
-        <v>99504</v>
+        <v>101403</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1936,21 +1936,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222857</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ekorrbär</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Maianthemum bifolium</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) F. W. Schmidt</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>431593</v>
+        <v>431550</v>
       </c>
       <c r="R13" t="n">
-        <v>6484647</v>
+        <v>6484628</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2030,16 +2030,16 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132976234</t>
+          <t>https://artportalen.se/Sighting/132976246</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129282017</v>
+        <v>132976234</v>
       </c>
       <c r="B14" t="n">
-        <v>87372</v>
+        <v>99504</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2047,34 +2047,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>249255</v>
+        <v>222857</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brun purpurspindling</t>
+          <t>Ekorrbär</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius subpurpurascens</t>
+          <t>Maianthemum bifolium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch) E.Berger</t>
+          <t>(L.) F. W. Schmidt</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ingasäter Norr, Vg</t>
+          <t>Ingasäter NO om, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>431599</v>
+        <v>431593</v>
       </c>
       <c r="R14" t="n">
-        <v>6484681</v>
+        <v>6484647</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2101,17 +2101,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Skifte med mycket blåsippa och hassel, ek och även skogslind</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2122,20 +2117,136 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Lösvkogsområde</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132976234</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129282017</v>
+      </c>
+      <c r="B15" t="n">
+        <v>87372</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>249255</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Brun purpurspindling</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cortinarius subpurpurascens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Batsch) E.Berger</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ingasäter Norr, Vg</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>431599</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6484681</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Skifte med mycket blåsippa och hassel, ek och även skogslind</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
           <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr">
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129282017</t>
         </is>
@@ -2156,6 +2267,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28715-2026 artfynd.xlsx
+++ b/artfynd/A 28715-2026 artfynd.xlsx
@@ -1484,7 +1484,7 @@
         <v>136441920</v>
       </c>
       <c r="B9" t="n">
-        <v>107039</v>
+        <v>107052</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 28715-2026 artfynd.xlsx
+++ b/artfynd/A 28715-2026 artfynd.xlsx
@@ -1484,7 +1484,7 @@
         <v>136441920</v>
       </c>
       <c r="B9" t="n">
-        <v>107052</v>
+        <v>107053</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
